--- a/survey_templates/026_cosmetic_surgery_survey--survey_templates.xlsx
+++ b/survey_templates/026_cosmetic_surgery_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_trend</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey_Trend</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please rate your overall experience with the surgery.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Patient_Satisfaction</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Patient Satisfaction</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate your satisfaction with the outcome of the surgery.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>expectations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Overall_Experience</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Expectations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What were your expectations before the surgery?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,112 +596,132 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>on_time_performance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>On-Time Performance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Was the surgery performed on time?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>surgeon_expertise</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Surgeon Expertise</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rate the surgeon's expertise.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Recommend</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Would you recommend the surgery to others?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate your overall rating of the surgery out of 5.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>complications</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Complications</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Were there any unexpected complications during the surgery?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_trend_1</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select_Trend_1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate your satisfaction with the recovery process.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_trend_2</t>
+          <t>post_surgery_care</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select_Trend_2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Post-Surgery Care</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Was the post-operative care adequate?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_trend_3</t>
+          <t>meet_expectations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select_Trend_3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Meet Expectations</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Did the surgery meet your expectations?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_trend_4</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select_Trend_4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or concerns.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>select_trend_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Select_Trend_5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>select_trend_6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Select_Trend_6</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>select_trend_7</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select_Trend_7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>select_trend_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select_Trend_8</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>select_trend_9</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select_Trend_9</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>select_trend_10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select_Trend_10</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +875,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_trend_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_trend_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_satisfaction_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_satisfaction_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1199,352 +948,403 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_trend_1_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_trend_1_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_trend_2_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_trend_2_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_trend_3_choices</t>
+          <t>on_time_performance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_trend_3_choices</t>
+          <t>on_time_performance_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_trend_4_choices</t>
+          <t>surgeon_expertise_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_trend_4_choices</t>
+          <t>surgeon_expertise_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_trend_5_choices</t>
+          <t>surgeon_expertise_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_trend_5_choices</t>
+          <t>surgeon_expertise_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_trend_6_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_trend_6_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_trend_7_choices</t>
+          <t>complications_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_trend_7_choices</t>
+          <t>complications_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_trend_8_choices</t>
+          <t>recovery_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_trend_8_choices</t>
+          <t>recovery_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_trend_9_choices</t>
+          <t>recovery_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_trend_9_choices</t>
+          <t>recovery_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_trend_10_choices</t>
+          <t>recovery_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_trend_10_choices</t>
+          <t>post_surgery_care_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>post_surgery_care_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>meet_expectations_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>meet_expectations_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
